--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0EE860-D9FC-4C6D-A845-BBCEE5CAEFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F8A7AF-0654-49BA-B1C0-3478F870F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -119,6 +119,14 @@
   </si>
   <si>
     <t>在社区中心冗余道具时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portContainerItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在港口集装箱时的倍率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,19 +466,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,7 +499,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -512,7 +520,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -533,7 +541,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -554,7 +562,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -568,7 +576,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -582,7 +590,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -596,7 +604,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -610,7 +618,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -624,7 +632,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -638,7 +646,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -652,18 +660,32 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>8</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>7500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="3">
+        <v>7000</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F8A7AF-0654-49BA-B1C0-3478F870F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380BD06B-8857-4751-BF29-385CD46FC5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +127,22 @@
   </si>
   <si>
     <t>在港口集装箱时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exchangeLeft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兑换面板左侧的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exchangeRight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兑换面板右侧的倍率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -466,19 +482,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="64.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="21.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +515,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -520,7 +536,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -541,7 +557,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -562,7 +578,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -576,7 +592,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -590,7 +606,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -604,7 +620,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -618,7 +634,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -632,7 +648,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -646,7 +662,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -660,7 +676,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -674,18 +690,46 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>9</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>7000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="2">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="3">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
